--- a/artfynd/A 21360-2021 artfynd.xlsx
+++ b/artfynd/A 21360-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118047752</v>
+        <v>118047984</v>
       </c>
       <c r="B2" t="n">
         <v>97836</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -731,10 +731,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581055</v>
+        <v>581006</v>
       </c>
       <c r="R2" t="n">
-        <v>7012241</v>
+        <v>7012209</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -794,7 +794,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118047522</v>
+        <v>118047820</v>
       </c>
       <c r="B3" t="n">
         <v>97836</v>
@@ -829,7 +829,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>130</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581203</v>
+        <v>580930</v>
       </c>
       <c r="R3" t="n">
-        <v>7012328</v>
+        <v>7012258</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -913,7 +913,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118047928</v>
+        <v>118047610</v>
       </c>
       <c r="B4" t="n">
         <v>97836</v>
@@ -948,7 +948,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -969,10 +969,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580993</v>
+        <v>581106</v>
       </c>
       <c r="R4" t="n">
-        <v>7012229</v>
+        <v>7012290</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1032,7 +1032,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118047688</v>
+        <v>118047955</v>
       </c>
       <c r="B5" t="n">
         <v>97836</v>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1088,10 +1088,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581097</v>
+        <v>581008</v>
       </c>
       <c r="R5" t="n">
-        <v>7012276</v>
+        <v>7012221</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1151,7 +1151,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118047967</v>
+        <v>118047771</v>
       </c>
       <c r="B6" t="n">
         <v>97836</v>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581017</v>
+        <v>581039</v>
       </c>
       <c r="R6" t="n">
-        <v>7012213</v>
+        <v>7012250</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1270,7 +1270,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118047897</v>
+        <v>118047845</v>
       </c>
       <c r="B7" t="n">
         <v>97836</v>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1326,10 +1326,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580995</v>
+        <v>580972</v>
       </c>
       <c r="R7" t="n">
-        <v>7012236</v>
+        <v>7012239</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118047633</v>
+        <v>118047500</v>
       </c>
       <c r="B8" t="n">
         <v>97836</v>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581099</v>
+        <v>581223</v>
       </c>
       <c r="R8" t="n">
-        <v>7012293</v>
+        <v>7012349</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1508,7 +1508,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118048037</v>
+        <v>118047688</v>
       </c>
       <c r="B9" t="n">
         <v>97836</v>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580990</v>
+        <v>581097</v>
       </c>
       <c r="R9" t="n">
-        <v>7012180</v>
+        <v>7012276</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1627,7 +1627,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118047866</v>
+        <v>118047796</v>
       </c>
       <c r="B10" t="n">
         <v>97836</v>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580985</v>
+        <v>581035</v>
       </c>
       <c r="R10" t="n">
-        <v>7012236</v>
+        <v>7012267</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1746,7 +1746,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118048015</v>
+        <v>118047909</v>
       </c>
       <c r="B11" t="n">
         <v>97836</v>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1802,10 +1802,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580968</v>
+        <v>581008</v>
       </c>
       <c r="R11" t="n">
-        <v>7012184</v>
+        <v>7012237</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1865,7 +1865,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118047886</v>
+        <v>118048037</v>
       </c>
       <c r="B12" t="n">
         <v>97836</v>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580987</v>
+        <v>580990</v>
       </c>
       <c r="R12" t="n">
-        <v>7012238</v>
+        <v>7012180</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1984,7 +1984,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118047736</v>
+        <v>118047928</v>
       </c>
       <c r="B13" t="n">
         <v>97836</v>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>130</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581038</v>
+        <v>580993</v>
       </c>
       <c r="R13" t="n">
-        <v>7012222</v>
+        <v>7012229</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118047462</v>
+        <v>118047778</v>
       </c>
       <c r="B14" t="n">
         <v>97836</v>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2159,10 +2159,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581226</v>
+        <v>581019</v>
       </c>
       <c r="R14" t="n">
-        <v>7012354</v>
+        <v>7012249</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2222,7 +2222,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118047955</v>
+        <v>118047897</v>
       </c>
       <c r="B15" t="n">
         <v>97836</v>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581008</v>
+        <v>580995</v>
       </c>
       <c r="R15" t="n">
-        <v>7012221</v>
+        <v>7012236</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2341,7 +2341,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118047771</v>
+        <v>118047736</v>
       </c>
       <c r="B16" t="n">
         <v>97836</v>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2397,10 +2397,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581039</v>
+        <v>581038</v>
       </c>
       <c r="R16" t="n">
-        <v>7012250</v>
+        <v>7012222</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2460,7 +2460,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118047553</v>
+        <v>118047967</v>
       </c>
       <c r="B17" t="n">
         <v>97836</v>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581151</v>
+        <v>581017</v>
       </c>
       <c r="R17" t="n">
-        <v>7012291</v>
+        <v>7012213</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2579,7 +2579,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118047720</v>
+        <v>118047701</v>
       </c>
       <c r="B18" t="n">
         <v>97836</v>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2635,10 +2635,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581046</v>
+        <v>581094</v>
       </c>
       <c r="R18" t="n">
-        <v>7012204</v>
+        <v>7012233</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2698,7 +2698,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118047828</v>
+        <v>118047383</v>
       </c>
       <c r="B19" t="n">
         <v>97836</v>
@@ -2733,7 +2733,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580960</v>
+        <v>581242</v>
       </c>
       <c r="R19" t="n">
-        <v>7012235</v>
+        <v>7012372</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2817,7 +2817,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118047810</v>
+        <v>118047866</v>
       </c>
       <c r="B20" t="n">
         <v>97836</v>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>86</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580926</v>
+        <v>580985</v>
       </c>
       <c r="R20" t="n">
-        <v>7012257</v>
+        <v>7012236</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118047541</v>
+        <v>118047522</v>
       </c>
       <c r="B21" t="n">
         <v>97836</v>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2992,10 +2992,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581176</v>
+        <v>581203</v>
       </c>
       <c r="R21" t="n">
-        <v>7012255</v>
+        <v>7012328</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -3055,7 +3055,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118047984</v>
+        <v>118047720</v>
       </c>
       <c r="B22" t="n">
         <v>97836</v>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>63</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3111,10 +3111,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581006</v>
+        <v>581046</v>
       </c>
       <c r="R22" t="n">
-        <v>7012209</v>
+        <v>7012204</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3174,7 +3174,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118047796</v>
+        <v>118047553</v>
       </c>
       <c r="B23" t="n">
         <v>97836</v>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3230,10 +3230,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581035</v>
+        <v>581151</v>
       </c>
       <c r="R23" t="n">
-        <v>7012267</v>
+        <v>7012291</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3293,7 +3293,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118047820</v>
+        <v>118047828</v>
       </c>
       <c r="B24" t="n">
         <v>97836</v>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>580930</v>
+        <v>580960</v>
       </c>
       <c r="R24" t="n">
-        <v>7012258</v>
+        <v>7012235</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3412,7 +3412,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118047845</v>
+        <v>118047886</v>
       </c>
       <c r="B25" t="n">
         <v>97836</v>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3468,10 +3468,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580972</v>
+        <v>580987</v>
       </c>
       <c r="R25" t="n">
-        <v>7012239</v>
+        <v>7012238</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3531,7 +3531,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118047909</v>
+        <v>118047752</v>
       </c>
       <c r="B26" t="n">
         <v>97836</v>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581008</v>
+        <v>581055</v>
       </c>
       <c r="R26" t="n">
-        <v>7012237</v>
+        <v>7012241</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3650,7 +3650,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118047383</v>
+        <v>118047810</v>
       </c>
       <c r="B27" t="n">
         <v>97836</v>
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581242</v>
+        <v>580926</v>
       </c>
       <c r="R27" t="n">
-        <v>7012372</v>
+        <v>7012257</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3769,7 +3769,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118047778</v>
+        <v>118047633</v>
       </c>
       <c r="B28" t="n">
         <v>97836</v>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581019</v>
+        <v>581099</v>
       </c>
       <c r="R28" t="n">
-        <v>7012249</v>
+        <v>7012293</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3888,7 +3888,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118047500</v>
+        <v>118047462</v>
       </c>
       <c r="B29" t="n">
         <v>97836</v>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3944,10 +3944,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>581223</v>
+        <v>581226</v>
       </c>
       <c r="R29" t="n">
-        <v>7012349</v>
+        <v>7012354</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -4007,7 +4007,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118047610</v>
+        <v>118048015</v>
       </c>
       <c r="B30" t="n">
         <v>97836</v>
@@ -4042,7 +4042,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4063,10 +4063,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>581106</v>
+        <v>580968</v>
       </c>
       <c r="R30" t="n">
-        <v>7012290</v>
+        <v>7012184</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -4126,7 +4126,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118047701</v>
+        <v>118047541</v>
       </c>
       <c r="B31" t="n">
         <v>97836</v>
@@ -4161,7 +4161,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4182,10 +4182,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581094</v>
+        <v>581176</v>
       </c>
       <c r="R31" t="n">
-        <v>7012233</v>
+        <v>7012255</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>

--- a/artfynd/A 21360-2021 artfynd.xlsx
+++ b/artfynd/A 21360-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118047984</v>
+        <v>118047500</v>
       </c>
       <c r="B2" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -731,10 +731,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581006</v>
+        <v>581223</v>
       </c>
       <c r="R2" t="n">
-        <v>7012209</v>
+        <v>7012349</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118047820</v>
+        <v>118047462</v>
       </c>
       <c r="B3" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580930</v>
+        <v>581226</v>
       </c>
       <c r="R3" t="n">
-        <v>7012258</v>
+        <v>7012354</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118047610</v>
+        <v>118047778</v>
       </c>
       <c r="B4" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -969,10 +969,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581106</v>
+        <v>581019</v>
       </c>
       <c r="R4" t="n">
-        <v>7012290</v>
+        <v>7012249</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1032,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118047955</v>
+        <v>118047909</v>
       </c>
       <c r="B5" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1091,7 +1091,7 @@
         <v>581008</v>
       </c>
       <c r="R5" t="n">
-        <v>7012221</v>
+        <v>7012237</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1151,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118047771</v>
+        <v>118047886</v>
       </c>
       <c r="B6" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581039</v>
+        <v>580987</v>
       </c>
       <c r="R6" t="n">
-        <v>7012250</v>
+        <v>7012238</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1270,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118047845</v>
+        <v>118047955</v>
       </c>
       <c r="B7" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1326,10 +1326,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580972</v>
+        <v>581008</v>
       </c>
       <c r="R7" t="n">
-        <v>7012239</v>
+        <v>7012221</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118047500</v>
+        <v>118047810</v>
       </c>
       <c r="B8" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581223</v>
+        <v>580926</v>
       </c>
       <c r="R8" t="n">
-        <v>7012349</v>
+        <v>7012257</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1508,10 +1508,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118047688</v>
+        <v>118047522</v>
       </c>
       <c r="B9" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581097</v>
+        <v>581203</v>
       </c>
       <c r="R9" t="n">
-        <v>7012276</v>
+        <v>7012328</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1627,10 +1627,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118047796</v>
+        <v>118047928</v>
       </c>
       <c r="B10" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>130</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581035</v>
+        <v>580993</v>
       </c>
       <c r="R10" t="n">
-        <v>7012267</v>
+        <v>7012229</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1746,10 +1746,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118047909</v>
+        <v>118047720</v>
       </c>
       <c r="B11" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>63</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1802,10 +1802,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581008</v>
+        <v>581046</v>
       </c>
       <c r="R11" t="n">
-        <v>7012237</v>
+        <v>7012204</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1865,10 +1865,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118048037</v>
+        <v>118047984</v>
       </c>
       <c r="B12" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580990</v>
+        <v>581006</v>
       </c>
       <c r="R12" t="n">
-        <v>7012180</v>
+        <v>7012209</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118047928</v>
+        <v>118047897</v>
       </c>
       <c r="B13" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580993</v>
+        <v>580995</v>
       </c>
       <c r="R13" t="n">
-        <v>7012229</v>
+        <v>7012236</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118047778</v>
+        <v>118047701</v>
       </c>
       <c r="B14" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2159,10 +2159,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581019</v>
+        <v>581094</v>
       </c>
       <c r="R14" t="n">
-        <v>7012249</v>
+        <v>7012233</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2222,10 +2222,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118047897</v>
+        <v>118047383</v>
       </c>
       <c r="B15" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580995</v>
+        <v>581242</v>
       </c>
       <c r="R15" t="n">
-        <v>7012236</v>
+        <v>7012372</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2341,10 +2341,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118047736</v>
+        <v>118048015</v>
       </c>
       <c r="B16" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2397,10 +2397,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581038</v>
+        <v>580968</v>
       </c>
       <c r="R16" t="n">
-        <v>7012222</v>
+        <v>7012184</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118047967</v>
+        <v>118047796</v>
       </c>
       <c r="B17" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581017</v>
+        <v>581035</v>
       </c>
       <c r="R17" t="n">
-        <v>7012213</v>
+        <v>7012267</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2579,10 +2579,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118047701</v>
+        <v>118047541</v>
       </c>
       <c r="B18" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2635,10 +2635,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581094</v>
+        <v>581176</v>
       </c>
       <c r="R18" t="n">
-        <v>7012233</v>
+        <v>7012255</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118047383</v>
+        <v>118047866</v>
       </c>
       <c r="B19" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>86</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581242</v>
+        <v>580985</v>
       </c>
       <c r="R19" t="n">
-        <v>7012372</v>
+        <v>7012236</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118047866</v>
+        <v>118047828</v>
       </c>
       <c r="B20" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580985</v>
+        <v>580960</v>
       </c>
       <c r="R20" t="n">
-        <v>7012236</v>
+        <v>7012235</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2936,10 +2936,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118047522</v>
+        <v>118047967</v>
       </c>
       <c r="B21" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2992,10 +2992,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581203</v>
+        <v>581017</v>
       </c>
       <c r="R21" t="n">
-        <v>7012328</v>
+        <v>7012213</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -3055,10 +3055,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118047720</v>
+        <v>118047688</v>
       </c>
       <c r="B22" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3111,10 +3111,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581046</v>
+        <v>581097</v>
       </c>
       <c r="R22" t="n">
-        <v>7012204</v>
+        <v>7012276</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3174,10 +3174,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118047553</v>
+        <v>118047752</v>
       </c>
       <c r="B23" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3230,10 +3230,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581151</v>
+        <v>581055</v>
       </c>
       <c r="R23" t="n">
-        <v>7012291</v>
+        <v>7012241</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3293,10 +3293,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118047828</v>
+        <v>118047610</v>
       </c>
       <c r="B24" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>580960</v>
+        <v>581106</v>
       </c>
       <c r="R24" t="n">
-        <v>7012235</v>
+        <v>7012290</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3412,10 +3412,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118047886</v>
+        <v>118047771</v>
       </c>
       <c r="B25" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3468,10 +3468,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580987</v>
+        <v>581039</v>
       </c>
       <c r="R25" t="n">
-        <v>7012238</v>
+        <v>7012250</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3531,10 +3531,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118047752</v>
+        <v>118047553</v>
       </c>
       <c r="B26" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581055</v>
+        <v>581151</v>
       </c>
       <c r="R26" t="n">
-        <v>7012241</v>
+        <v>7012291</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3650,10 +3650,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118047810</v>
+        <v>118047845</v>
       </c>
       <c r="B27" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580926</v>
+        <v>580972</v>
       </c>
       <c r="R27" t="n">
-        <v>7012257</v>
+        <v>7012239</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3769,10 +3769,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118047633</v>
+        <v>118047820</v>
       </c>
       <c r="B28" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>130</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581099</v>
+        <v>580930</v>
       </c>
       <c r="R28" t="n">
-        <v>7012293</v>
+        <v>7012258</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3888,10 +3888,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118047462</v>
+        <v>118047633</v>
       </c>
       <c r="B29" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3944,10 +3944,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>581226</v>
+        <v>581099</v>
       </c>
       <c r="R29" t="n">
-        <v>7012354</v>
+        <v>7012293</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -4007,10 +4007,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118048015</v>
+        <v>118047736</v>
       </c>
       <c r="B30" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4063,10 +4063,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580968</v>
+        <v>581038</v>
       </c>
       <c r="R30" t="n">
-        <v>7012184</v>
+        <v>7012222</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -4126,10 +4126,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118047541</v>
+        <v>118048037</v>
       </c>
       <c r="B31" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4182,10 +4182,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581176</v>
+        <v>580990</v>
       </c>
       <c r="R31" t="n">
-        <v>7012255</v>
+        <v>7012180</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>

--- a/artfynd/A 21360-2021 artfynd.xlsx
+++ b/artfynd/A 21360-2021 artfynd.xlsx
@@ -3293,7 +3293,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118047610</v>
+        <v>118047771</v>
       </c>
       <c r="B24" t="n">
         <v>97838</v>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581106</v>
+        <v>581039</v>
       </c>
       <c r="R24" t="n">
-        <v>7012290</v>
+        <v>7012250</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3412,7 +3412,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118047771</v>
+        <v>118047610</v>
       </c>
       <c r="B25" t="n">
         <v>97838</v>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3468,10 +3468,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581039</v>
+        <v>581106</v>
       </c>
       <c r="R25" t="n">
-        <v>7012250</v>
+        <v>7012290</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
